--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-08-31 / 2025-09-06</t>
+          <t>Ventas 2025-09-07 / 2025-09-13</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>42201.23</v>
+        <v>36894.18</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4990</v>
+        <v>4690</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>17148.27</v>
+        <v>15437.32</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2292</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>8194.99</v>
+        <v>8416.9</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1075</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>23559.42</v>
+        <v>22139.54</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>3022</v>
+        <v>2903</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>8743.42</v>
+        <v>8114.41</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1134</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>27648.11</v>
+        <v>29748.28</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>2995</v>
+        <v>3358</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>30095.58</v>
+        <v>27829.16</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3643</v>
+        <v>3535</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-07 / 2025-09-13</t>
+          <t>Ventas 2025-09-14 / 2025-09-20</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>36894.18</v>
+        <v>39099.32</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4690</v>
+        <v>4975</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>15437.32</v>
+        <v>16643.92</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2081</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>8416.9</v>
+        <v>9025.629999999999</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1167</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>22139.54</v>
+        <v>21709.43</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>2903</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>8114.41</v>
+        <v>6737.1</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>1112</v>
+        <v>884</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>29748.28</v>
+        <v>30786.64</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3358</v>
+        <v>3442</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>27829.16</v>
+        <v>27318.85</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3535</v>
+        <v>3484</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-14 / 2025-09-20</t>
+          <t>Ventas 2025-09-21 / 2025-09-27</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>39099.32</v>
+        <v>36689.17</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4975</v>
+        <v>4588</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>16643.92</v>
+        <v>16604.63</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2263</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>9025.629999999999</v>
+        <v>8334.6</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1275</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>21709.43</v>
+        <v>21011.18</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>2887</v>
+        <v>2761</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>6737.1</v>
+        <v>6216.96</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>884</v>
+        <v>845</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>30786.64</v>
+        <v>29171.99</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3442</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>27318.85</v>
+        <v>26915.63</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3484</v>
+        <v>3461</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-21 / 2025-09-27</t>
+          <t>Ventas 2025-09-28 / 2025-10-04</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>36689.17</v>
+        <v>39551.65</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4588</v>
+        <v>4845</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>16604.63</v>
+        <v>15727.36</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2259</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>8334.6</v>
+        <v>7493.51</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1080</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>21011.18</v>
+        <v>19403.59</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>2761</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>6216.96</v>
+        <v>6219.48</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>845</v>
+        <v>840</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>29171.99</v>
+        <v>29979.55</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3318</v>
+        <v>3342</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>26915.63</v>
+        <v>24128.62</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3461</v>
+        <v>3119</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-09-28 / 2025-10-04</t>
+          <t>Ventas 2025-10-05 / 2025-10-11</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>39551.65</v>
+        <v>35362.54</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4845</v>
+        <v>4389</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>15727.36</v>
+        <v>15028.8</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2216</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>7493.51</v>
+        <v>6696.18</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1015</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>19403.59</v>
+        <v>18514.18</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>2603</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>6219.48</v>
+        <v>5594.93</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>840</v>
+        <v>760</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>29979.55</v>
+        <v>32880.36</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3342</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>24128.62</v>
+        <v>23202.94</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3119</v>
+        <v>2970</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-05 / 2025-10-11</t>
+          <t>Ventas 2025-10-12 / 2025-10-18</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>35362.54</v>
+        <v>33301.91</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4389</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>15028.8</v>
+        <v>14211.8</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>2145</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>6696.18</v>
+        <v>8162.46</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>929</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>18514.18</v>
+        <v>18970.68</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>2497</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>5594.93</v>
+        <v>6453.69</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>760</v>
+        <v>886</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>32880.36</v>
+        <v>30370.91</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3578</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>23202.94</v>
+        <v>24436.55</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>2970</v>
+        <v>3018</v>
       </c>
     </row>
   </sheetData>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ventas 2025-10-12 / 2025-10-18</t>
+          <t>Ventas 2025-10-19 / 2025-10-25</t>
         </is>
       </c>
     </row>
@@ -467,12 +467,12 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>33301.91</v>
+        <v>36833.76</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>4184</v>
+        <v>4519</v>
       </c>
     </row>
     <row r="5">
@@ -483,12 +483,12 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>14211.8</v>
+        <v>17563.66</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>1974</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="6">
@@ -499,12 +499,12 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>8162.46</v>
+        <v>7517</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>1110</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="7">
@@ -531,12 +531,12 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>18970.68</v>
+        <v>20331.91</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>2484</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="9">
@@ -547,12 +547,12 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>6453.69</v>
+        <v>5898.68</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>886</v>
+        <v>802</v>
       </c>
     </row>
     <row r="10">
@@ -563,12 +563,12 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>30370.91</v>
+        <v>31268.73</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>3292</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="11">
@@ -579,12 +579,12 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>24436.55</v>
+        <v>27692.25</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>3018</v>
+        <v>3415</v>
       </c>
     </row>
   </sheetData>
